--- a/Sheets/ops-primer-working-copy.xlsx
+++ b/Sheets/ops-primer-working-copy.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JonathanDeLaCruz\Documents\Revature\excel-primer\demo\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC8AB3B-341B-4CDD-8AA8-6748E03961F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80BEE60-60AF-488F-91EE-389915FA0C73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="12900" windowWidth="23256" windowHeight="12456" tabRatio="549" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="12900" windowWidth="23256" windowHeight="12456" tabRatio="549" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Agenda" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
     <sheet name="02_Formulas" sheetId="3" r:id="rId3"/>
     <sheet name="03_Checks" sheetId="4" r:id="rId4"/>
     <sheet name="04_Cleaning" sheetId="5" r:id="rId5"/>
-    <sheet name="Detail1" sheetId="11" r:id="rId6"/>
-    <sheet name="05a_ByClient" sheetId="10" r:id="rId7"/>
+    <sheet name="05a_ByClient" sheetId="10" r:id="rId6"/>
+    <sheet name="05b_Service" sheetId="12" r:id="rId7"/>
     <sheet name="05_Pivots" sheetId="6" r:id="rId8"/>
     <sheet name="06_Reconcile" sheetId="7" r:id="rId9"/>
     <sheet name="07_Lab_Tasks" sheetId="8" r:id="rId10"/>
@@ -27,12 +27,24 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'01_Foundations'!$A$1:$J$41</definedName>
+    <definedName name="Slicer_risk_rating">#N/A</definedName>
+    <definedName name="Slicer_txn_type">#N/A</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="17" r:id="rId12"/>
+    <pivotCache cacheId="2" r:id="rId12"/>
+    <pivotCache cacheId="7" r:id="rId13"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId14"/>
+        <x14:slicerCache r:id="rId15"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -71,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9957" uniqueCount="2355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9900" uniqueCount="2358">
   <si>
     <t>Ops Analyst Excel Primer - two days, one workbook</t>
   </si>
@@ -7135,7 +7147,16 @@
     <t>Count of amount</t>
   </si>
   <si>
-    <t>Details for Sum of amount - client_name: Aldridge Manufacturing, Months (txn_date): Feb</t>
+    <t>Sum of budget</t>
+  </si>
+  <si>
+    <t>Sum of actual_cost</t>
+  </si>
+  <si>
+    <t>Sum of variance</t>
+  </si>
+  <si>
+    <t>(All)</t>
   </si>
 </sst>
 </file>
@@ -7304,10 +7325,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -7392,6 +7410,167 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>28868</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>159327</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>530323</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>3663</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="txn_type">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C191ED2-C4EA-8A98-6B13-E3BC65247591}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="txn_type"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10477100" y="1903095"/>
+              <a:ext cx="1815732" cy="3531550"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>27403</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>188302</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>530323</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>118976</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="risk_rating">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19D84019-B3FE-BE87-07C7-74DD510BE1B1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="risk_rating"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10475635" y="382266"/>
+              <a:ext cx="1817197" cy="1482383"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7500,7 +7679,13 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="txn_type" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="5">
+        <s v="Wire"/>
+        <s v="Check"/>
+        <s v="Cash"/>
+        <s v="Card"/>
+        <s v="ACH"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="direction" numFmtId="0">
       <sharedItems/>
@@ -7553,7 +7738,11 @@
       </sharedItems>
     </cacheField>
     <cacheField name="risk_rating" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="3">
+        <s v="Low"/>
+        <s v="Medium"/>
+        <s v="High"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="Days (txn_date)" numFmtId="0" databaseField="0">
       <fieldGroup base="1">
@@ -7954,6 +8143,83 @@
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="1617725013"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Jonathan De La Cruz" refreshedDate="46280.397160300927" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="40" xr:uid="{BCBF5185-3C04-4B87-8791-8149847B1A42}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="tblEng03"/>
+  </cacheSource>
+  <cacheFields count="17">
+    <cacheField name="engagement_id" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="client_id" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="engagement_name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="service_line" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Audit"/>
+        <s v="Tax"/>
+        <s v="Advisory"/>
+        <s v="Risk Consulting"/>
+        <s v="Deal Advisory"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="manager" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="start_date" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-01-08T00:00:00" maxDate="2026-05-21T00:00:00"/>
+    </cacheField>
+    <cacheField name="end_date" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2026-03-17T00:00:00" maxDate="2026-11-22T00:00:00"/>
+    </cacheField>
+    <cacheField name="budget" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="45500" maxValue="478500"/>
+    </cacheField>
+    <cacheField name="actual_cost" numFmtId="3">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="41100" maxValue="530100"/>
+    </cacheField>
+    <cacheField name="status" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Active"/>
+        <s v="Complete"/>
+        <s v="On Hold"/>
+        <s v="Planned"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="variance" numFmtId="3">
+      <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="-95600" maxValue="139200"/>
+    </cacheField>
+    <cacheField name="margin_pct" numFmtId="165">
+      <sharedItems containsMixedTypes="1" containsNumber="1" minValue="-0.2201005025125628" maxValue="0.32066115702479336"/>
+    </cacheField>
+    <cacheField name="budget_with_uplift" numFmtId="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="48912.5" maxValue="514387.5"/>
+    </cacheField>
+    <cacheField name="client_name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="risk_rating" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="id_count" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="2"/>
+    </cacheField>
+    <cacheField name="id_ok" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
       <x14:pivotCacheDefinition/>
     </ext>
   </extLst>
@@ -7966,7 +8232,7 @@
     <s v="TX0001"/>
     <x v="0"/>
     <s v="CLI-001"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="7477"/>
     <s v="USD"/>
@@ -7975,13 +8241,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="0"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0002"/>
     <x v="0"/>
     <s v="CLI-016"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="17413"/>
     <s v="USD"/>
@@ -7990,13 +8256,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="1"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0003"/>
     <x v="1"/>
     <s v="CLI-002"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="2496"/>
     <s v="USD"/>
@@ -8005,13 +8271,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="2"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0004"/>
     <x v="1"/>
     <s v="CLI-016"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="2849"/>
     <s v="USD"/>
@@ -8020,13 +8286,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="1"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0005"/>
     <x v="1"/>
     <s v="CLI-019"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="5746"/>
     <s v="USD"/>
@@ -8035,13 +8301,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="3"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0006"/>
     <x v="1"/>
     <s v="CLI-001"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="6384"/>
     <s v="USD"/>
@@ -8050,13 +8316,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="0"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0007"/>
     <x v="2"/>
     <s v="CLI-010"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="13557"/>
     <s v="USD"/>
@@ -8065,13 +8331,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="4"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0008"/>
     <x v="2"/>
     <s v="CLI-004"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="7082"/>
     <s v="USD"/>
@@ -8080,13 +8346,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="5"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0009"/>
     <x v="2"/>
     <s v="CLI-017"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="3771"/>
     <s v="USD"/>
@@ -8095,13 +8361,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="6"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0010"/>
     <x v="3"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="4648"/>
     <s v="USD"/>
@@ -8110,13 +8376,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0011"/>
     <x v="3"/>
     <s v="CLI-016"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="716"/>
     <s v="USD"/>
@@ -8125,13 +8391,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="1"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0012"/>
     <x v="3"/>
     <s v="CLI-001"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="1312"/>
     <s v="USD"/>
@@ -8140,13 +8406,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="0"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0013"/>
     <x v="3"/>
     <s v="CLI-022"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="5757"/>
     <s v="USD"/>
@@ -8155,13 +8421,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="8"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0014"/>
     <x v="3"/>
     <s v="CLI-012"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="3497"/>
     <s v="USD"/>
@@ -8170,13 +8436,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="9"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0015"/>
     <x v="3"/>
     <s v="CLI-014"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="22621"/>
     <s v="USD"/>
@@ -8185,13 +8451,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="10"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0016"/>
     <x v="4"/>
     <s v="CLI-013"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="7395"/>
     <s v="USD"/>
@@ -8200,13 +8466,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="11"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0017"/>
     <x v="4"/>
     <s v="CLI-006"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="3865"/>
     <s v="USD"/>
@@ -8215,13 +8481,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="12"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0018"/>
     <x v="4"/>
     <s v="CLI-006"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="1452"/>
     <s v="USD"/>
@@ -8230,13 +8496,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="12"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0019"/>
     <x v="4"/>
     <s v="CLI-023"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="12221"/>
     <s v="USD"/>
@@ -8245,13 +8511,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="13"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0020"/>
     <x v="4"/>
     <s v="CLI-025"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="4641"/>
     <s v="USD"/>
@@ -8260,13 +8526,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="14"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0021"/>
     <x v="4"/>
     <s v="CLI-005"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="1598"/>
     <s v="USD"/>
@@ -8275,13 +8541,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="15"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0022"/>
     <x v="5"/>
     <s v="CLI-012"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="8096"/>
     <s v="USD"/>
@@ -8290,13 +8556,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="9"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0023"/>
     <x v="5"/>
     <s v="CLI-003"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="4231"/>
     <s v="USD"/>
@@ -8305,13 +8571,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0024"/>
     <x v="5"/>
     <s v="CLI-014"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="4426"/>
     <s v="USD"/>
@@ -8320,13 +8586,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="10"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0025"/>
     <x v="5"/>
     <s v="CLI-012"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="9361"/>
     <s v="USD"/>
@@ -8335,13 +8601,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="9"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0026"/>
     <x v="6"/>
     <s v="CLI-011"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="1658"/>
     <s v="USD"/>
@@ -8350,13 +8616,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0027"/>
     <x v="6"/>
     <s v="CLI-015"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="6948"/>
     <s v="USD"/>
@@ -8365,13 +8631,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="18"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0028"/>
     <x v="7"/>
     <s v="CLI-015"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="882"/>
     <s v="USD"/>
@@ -8380,13 +8646,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="18"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0029"/>
     <x v="7"/>
     <s v="CLI-015"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="18317"/>
     <s v="USD"/>
@@ -8395,13 +8661,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="18"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0030"/>
     <x v="8"/>
     <s v="CLI-018"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="215"/>
     <s v="USD"/>
@@ -8410,13 +8676,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="19"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0031"/>
     <x v="9"/>
     <s v="CLI-020"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="9669"/>
     <s v="USD"/>
@@ -8425,13 +8691,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="20"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0032"/>
     <x v="9"/>
     <s v="CLI-003"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="1100"/>
     <s v="USD"/>
@@ -8440,13 +8706,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0033"/>
     <x v="9"/>
     <s v="CLI-004"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="1080"/>
     <s v="USD"/>
@@ -8455,13 +8721,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="5"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0034"/>
     <x v="10"/>
     <s v="CLI-019"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="1945"/>
     <s v="USD"/>
@@ -8470,13 +8736,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="3"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0035"/>
     <x v="10"/>
     <s v="CLI-019"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="13191"/>
     <s v="USD"/>
@@ -8485,13 +8751,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="3"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0036"/>
     <x v="11"/>
     <s v="CLI-003"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="12500"/>
     <s v="USD"/>
@@ -8500,13 +8766,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0037"/>
     <x v="11"/>
     <s v="CLI-022"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="472"/>
     <s v="USD"/>
@@ -8515,13 +8781,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="8"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0038"/>
     <x v="11"/>
     <s v="CLI-020"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="5831"/>
     <s v="USD"/>
@@ -8530,13 +8796,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="20"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0039"/>
     <x v="12"/>
     <s v="CLI-020"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="1684"/>
     <s v="USD"/>
@@ -8545,13 +8811,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="20"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0040"/>
     <x v="12"/>
     <s v="CLI-008"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="900"/>
     <s v="USD"/>
@@ -8560,13 +8826,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="21"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0041"/>
     <x v="12"/>
     <s v="CLI-023"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="5558"/>
     <s v="USD"/>
@@ -8575,13 +8841,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="13"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0042"/>
     <x v="13"/>
     <s v="CLI-017"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="1405"/>
     <s v="USD"/>
@@ -8590,13 +8856,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="6"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0043"/>
     <x v="14"/>
     <s v="CLI-007"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="6308"/>
     <s v="USD"/>
@@ -8605,13 +8871,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0044"/>
     <x v="14"/>
     <s v="CLI-022"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="2233"/>
     <s v="USD"/>
@@ -8620,13 +8886,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="8"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0045"/>
     <x v="15"/>
     <s v="CLI-016"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="1821"/>
     <s v="USD"/>
@@ -8635,13 +8901,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="1"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0046"/>
     <x v="15"/>
     <s v="CLI-015"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="2390"/>
     <s v="USD"/>
@@ -8650,13 +8916,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="18"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0047"/>
     <x v="16"/>
     <s v="CLI-006"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="3973"/>
     <s v="USD"/>
@@ -8665,13 +8931,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="12"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0048"/>
     <x v="16"/>
     <s v="CLI-008"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="84"/>
     <s v="USD"/>
@@ -8680,13 +8946,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="21"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0049"/>
     <x v="16"/>
     <s v="CLI-004"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="5204"/>
     <s v="USD"/>
@@ -8695,13 +8961,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="5"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0050"/>
     <x v="16"/>
     <s v="CLI-017"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="4838"/>
     <s v="USD"/>
@@ -8710,13 +8976,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="6"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0051"/>
     <x v="16"/>
     <s v="CLI-023"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="8511"/>
     <s v="USD"/>
@@ -8725,13 +8991,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="13"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0052"/>
     <x v="17"/>
     <s v="CLI-011"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="12674"/>
     <s v="USD"/>
@@ -8740,13 +9006,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0053"/>
     <x v="17"/>
     <s v="CLI-019"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="14035"/>
     <s v="USD"/>
@@ -8755,13 +9021,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="3"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0054"/>
     <x v="17"/>
     <s v="CLI-018"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="7720"/>
     <s v="USD"/>
@@ -8770,13 +9036,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="19"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0055"/>
     <x v="17"/>
     <s v="CLI-001"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="5666"/>
     <s v="USD"/>
@@ -8785,13 +9051,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="0"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0056"/>
     <x v="18"/>
     <s v="CLI-022"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="3784"/>
     <s v="USD"/>
@@ -8800,13 +9066,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="8"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0057"/>
     <x v="18"/>
     <s v="CLI-024"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="4699"/>
     <s v="USD"/>
@@ -8815,13 +9081,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="23"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0058"/>
     <x v="18"/>
     <s v="CLI-007"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="1123"/>
     <s v="USD"/>
@@ -8830,13 +9096,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0059"/>
     <x v="18"/>
     <s v="CLI-018"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="3319"/>
     <s v="USD"/>
@@ -8845,13 +9111,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="19"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0060"/>
     <x v="19"/>
     <s v="CLI-001"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="98"/>
     <s v="USD"/>
@@ -8860,13 +9126,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="0"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0061"/>
     <x v="19"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="1613"/>
     <s v="USD"/>
@@ -8875,13 +9141,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0062"/>
     <x v="19"/>
     <s v="CLI-012"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="463"/>
     <s v="USD"/>
@@ -8890,13 +9156,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="9"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0063"/>
     <x v="19"/>
     <s v="CLI-012"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="354"/>
     <s v="USD"/>
@@ -8905,13 +9171,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="9"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0064"/>
     <x v="20"/>
     <s v="CLI-019"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="1164"/>
     <s v="USD"/>
@@ -8920,13 +9186,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="3"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0065"/>
     <x v="20"/>
     <s v="CLI-005"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="18400"/>
     <s v="USD"/>
@@ -8935,13 +9201,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="15"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0066"/>
     <x v="20"/>
     <s v="CLI-022"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="13754"/>
     <s v="USD"/>
@@ -8950,13 +9216,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="8"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0067"/>
     <x v="20"/>
     <s v="CLI-011"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="21839"/>
     <s v="USD"/>
@@ -8965,13 +9231,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0068"/>
     <x v="20"/>
     <s v="CLI-003"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="769"/>
     <s v="USD"/>
@@ -8980,13 +9246,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0069"/>
     <x v="20"/>
     <s v="CLI-025"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="6484"/>
     <s v="USD"/>
@@ -8995,13 +9261,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="14"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0070"/>
     <x v="21"/>
     <s v="CLI-011"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="1799"/>
     <s v="USD"/>
@@ -9010,13 +9276,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0071"/>
     <x v="21"/>
     <s v="CLI-021"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="20052"/>
     <s v="USD"/>
@@ -9025,13 +9291,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="24"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0072"/>
     <x v="21"/>
     <s v="CLI-004"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="3989"/>
     <s v="USD"/>
@@ -9040,13 +9306,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="5"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0073"/>
     <x v="21"/>
     <s v="CLI-006"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="4362"/>
     <s v="USD"/>
@@ -9055,13 +9321,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="12"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0074"/>
     <x v="21"/>
     <s v="CLI-007"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="5038"/>
     <s v="USD"/>
@@ -9070,13 +9336,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0075"/>
     <x v="22"/>
     <s v="CLI-021"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="1677"/>
     <s v="USD"/>
@@ -9085,13 +9351,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="24"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0076"/>
     <x v="22"/>
     <s v="CLI-014"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="8019"/>
     <s v="USD"/>
@@ -9100,13 +9366,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="10"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0077"/>
     <x v="23"/>
     <s v="CLI-004"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="14069"/>
     <s v="USD"/>
@@ -9115,13 +9381,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="5"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0078"/>
     <x v="24"/>
     <s v="CLI-006"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="8587"/>
     <s v="USD"/>
@@ -9130,13 +9396,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="12"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0079"/>
     <x v="24"/>
     <s v="CLI-011"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="1688"/>
     <s v="USD"/>
@@ -9145,13 +9411,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0080"/>
     <x v="25"/>
     <s v="CLI-016"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="2398"/>
     <s v="USD"/>
@@ -9160,13 +9426,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="1"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0081"/>
     <x v="26"/>
     <s v="CLI-014"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="372"/>
     <s v="USD"/>
@@ -9175,13 +9441,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="10"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0082"/>
     <x v="27"/>
     <s v="CLI-020"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="17482"/>
     <s v="USD"/>
@@ -9190,13 +9456,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="20"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0083"/>
     <x v="27"/>
     <s v="CLI-003"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="9817"/>
     <s v="USD"/>
@@ -9205,13 +9471,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0084"/>
     <x v="28"/>
     <s v="CLI-007"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="10000"/>
     <s v="USD"/>
@@ -9220,13 +9486,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0085"/>
     <x v="28"/>
     <s v="CLI-002"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="7048"/>
     <s v="USD"/>
@@ -9235,13 +9501,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="2"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0086"/>
     <x v="29"/>
     <s v="CLI-008"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="1417"/>
     <s v="USD"/>
@@ -9250,13 +9516,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="21"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0087"/>
     <x v="29"/>
     <s v="CLI-011"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="2184"/>
     <s v="USD"/>
@@ -9265,13 +9531,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0088"/>
     <x v="30"/>
     <s v="CLI-006"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="1782"/>
     <s v="USD"/>
@@ -9280,13 +9546,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="12"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0089"/>
     <x v="30"/>
     <s v="CLI-024"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="1526"/>
     <s v="USD"/>
@@ -9295,13 +9561,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="23"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0090"/>
     <x v="30"/>
     <s v="CLI-024"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="7096"/>
     <s v="USD"/>
@@ -9310,13 +9576,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="23"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0091"/>
     <x v="30"/>
     <s v="CLI-010"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="3376"/>
     <s v="USD"/>
@@ -9325,13 +9591,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="4"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0092"/>
     <x v="30"/>
     <s v="CLI-023"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="14336"/>
     <s v="USD"/>
@@ -9340,13 +9606,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="13"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0093"/>
     <x v="30"/>
     <s v="CLI-008"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="2229"/>
     <s v="USD"/>
@@ -9355,13 +9621,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="21"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0094"/>
     <x v="30"/>
     <s v="CLI-011"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="3885"/>
     <s v="USD"/>
@@ -9370,13 +9636,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0095"/>
     <x v="31"/>
     <s v="CLI-004"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="19661"/>
     <s v="USD"/>
@@ -9385,13 +9651,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="5"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0096"/>
     <x v="31"/>
     <s v="CLI-002"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="22677"/>
     <s v="USD"/>
@@ -9400,13 +9666,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="2"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0097"/>
     <x v="31"/>
     <s v="CLI-015"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="955"/>
     <s v="USD"/>
@@ -9415,13 +9681,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="18"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0098"/>
     <x v="32"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="495"/>
     <s v="USD"/>
@@ -9430,13 +9696,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0099"/>
     <x v="32"/>
     <s v="CLI-017"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="16306"/>
     <s v="USD"/>
@@ -9445,13 +9711,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="6"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0100"/>
     <x v="32"/>
     <s v="CLI-003"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="1402"/>
     <s v="USD"/>
@@ -9460,13 +9726,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0101"/>
     <x v="32"/>
     <s v="CLI-007"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="9400"/>
     <s v="USD"/>
@@ -9475,13 +9741,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0102"/>
     <x v="32"/>
     <s v="CLI-013"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="800"/>
     <s v="USD"/>
@@ -9490,13 +9756,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="11"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0103"/>
     <x v="32"/>
     <s v="CLI-013"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="9479"/>
     <s v="USD"/>
@@ -9505,13 +9771,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="11"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0104"/>
     <x v="33"/>
     <s v="CLI-021"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="6713"/>
     <s v="USD"/>
@@ -9520,13 +9786,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="24"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0105"/>
     <x v="33"/>
     <s v="CLI-021"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="8366"/>
     <s v="USD"/>
@@ -9535,13 +9801,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="24"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0106"/>
     <x v="33"/>
     <s v="CLI-024"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="1114"/>
     <s v="USD"/>
@@ -9550,13 +9816,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="23"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0107"/>
     <x v="33"/>
     <s v="CLI-007"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="4012"/>
     <s v="USD"/>
@@ -9565,13 +9831,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0108"/>
     <x v="33"/>
     <s v="CLI-022"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="16529"/>
     <s v="USD"/>
@@ -9580,13 +9846,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="8"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0109"/>
     <x v="33"/>
     <s v="CLI-018"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="2221"/>
     <s v="USD"/>
@@ -9595,13 +9861,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="19"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0110"/>
     <x v="33"/>
     <s v="CLI-012"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="488"/>
     <s v="USD"/>
@@ -9610,13 +9876,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="9"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0111"/>
     <x v="33"/>
     <s v="CLI-008"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="2219"/>
     <s v="USD"/>
@@ -9625,13 +9891,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="21"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0112"/>
     <x v="34"/>
     <s v="CLI-016"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="82"/>
     <s v="USD"/>
@@ -9640,13 +9906,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="1"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0113"/>
     <x v="34"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="533"/>
     <s v="USD"/>
@@ -9655,13 +9921,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0114"/>
     <x v="34"/>
     <s v="CLI-022"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="1296"/>
     <s v="USD"/>
@@ -9670,13 +9936,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="8"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0115"/>
     <x v="34"/>
     <s v="CLI-018"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="16125"/>
     <s v="USD"/>
@@ -9685,13 +9951,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="19"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0116"/>
     <x v="35"/>
     <s v="CLI-024"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="3071"/>
     <s v="USD"/>
@@ -9700,13 +9966,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="23"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0117"/>
     <x v="35"/>
     <s v="CLI-007"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="9650"/>
     <s v="USD"/>
@@ -9715,13 +9981,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0118"/>
     <x v="36"/>
     <s v="CLI-006"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="2372"/>
     <s v="USD"/>
@@ -9730,13 +9996,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="12"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0119"/>
     <x v="36"/>
     <s v="CLI-003"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="13414"/>
     <s v="USD"/>
@@ -9745,13 +10011,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0120"/>
     <x v="36"/>
     <s v="CLI-020"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="5642"/>
     <s v="USD"/>
@@ -9760,13 +10026,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="20"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0121"/>
     <x v="37"/>
     <s v="CLI-010"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="2767"/>
     <s v="USD"/>
@@ -9775,13 +10041,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="4"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0122"/>
     <x v="37"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="26750"/>
     <s v="USD"/>
@@ -9790,13 +10056,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0123"/>
     <x v="37"/>
     <s v="CLI-022"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="7318"/>
     <s v="USD"/>
@@ -9805,13 +10071,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="8"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0124"/>
     <x v="37"/>
     <s v="CLI-003"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="9040"/>
     <s v="USD"/>
@@ -9820,13 +10086,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0125"/>
     <x v="38"/>
     <s v="CLI-021"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="5408"/>
     <s v="USD"/>
@@ -9835,13 +10101,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="24"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0126"/>
     <x v="38"/>
     <s v="CLI-007"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="9800"/>
     <s v="USD"/>
@@ -9850,13 +10116,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0127"/>
     <x v="38"/>
     <s v="CLI-023"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="1633"/>
     <s v="USD"/>
@@ -9865,13 +10131,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="13"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0128"/>
     <x v="38"/>
     <s v="CLI-021"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="5861"/>
     <s v="USD"/>
@@ -9880,13 +10146,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="24"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0129"/>
     <x v="39"/>
     <s v="CLI-008"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="5128"/>
     <s v="USD"/>
@@ -9895,13 +10161,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="21"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0130"/>
     <x v="39"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="17854"/>
     <s v="USD"/>
@@ -9910,13 +10176,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0131"/>
     <x v="39"/>
     <s v="CLI-005"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="1531"/>
     <s v="USD"/>
@@ -9925,13 +10191,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="15"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0132"/>
     <x v="40"/>
     <s v="CLI-012"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="2083"/>
     <s v="USD"/>
@@ -9940,13 +10206,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="9"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0133"/>
     <x v="40"/>
     <s v="CLI-013"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="1627"/>
     <s v="USD"/>
@@ -9955,13 +10221,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="11"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0134"/>
     <x v="40"/>
     <s v="CLI-008"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="448"/>
     <s v="USD"/>
@@ -9970,13 +10236,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="21"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0135"/>
     <x v="41"/>
     <s v="CLI-007"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="9550"/>
     <s v="USD"/>
@@ -9985,13 +10251,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0136"/>
     <x v="41"/>
     <s v="CLI-007"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="4516"/>
     <s v="USD"/>
@@ -10000,13 +10266,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0137"/>
     <x v="42"/>
     <s v="CLI-017"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="18575"/>
     <s v="USD"/>
@@ -10015,13 +10281,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="6"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0138"/>
     <x v="42"/>
     <s v="CLI-001"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="8706"/>
     <s v="USD"/>
@@ -10030,13 +10296,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="0"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0139"/>
     <x v="42"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="3511"/>
     <s v="USD"/>
@@ -10045,13 +10311,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0140"/>
     <x v="43"/>
     <s v="CLI-017"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="19115"/>
     <s v="USD"/>
@@ -10060,13 +10326,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="6"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0141"/>
     <x v="43"/>
     <s v="CLI-005"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="1412"/>
     <s v="USD"/>
@@ -10075,13 +10341,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="15"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0142"/>
     <x v="43"/>
     <s v="CLI-025"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="621"/>
     <s v="USD"/>
@@ -10090,13 +10356,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="14"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0143"/>
     <x v="44"/>
     <s v="CLI-002"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="565"/>
     <s v="USD"/>
@@ -10105,13 +10371,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="2"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0144"/>
     <x v="44"/>
     <s v="CLI-024"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="2214"/>
     <s v="USD"/>
@@ -10120,13 +10386,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="23"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0145"/>
     <x v="44"/>
     <s v="CLI-007"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="9750"/>
     <s v="USD"/>
@@ -10135,13 +10401,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0146"/>
     <x v="44"/>
     <s v="CLI-008"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="2425"/>
     <s v="USD"/>
@@ -10150,13 +10416,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="21"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0147"/>
     <x v="44"/>
     <s v="CLI-016"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="18042"/>
     <s v="USD"/>
@@ -10165,13 +10431,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="1"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0148"/>
     <x v="44"/>
     <s v="CLI-019"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="2060"/>
     <s v="USD"/>
@@ -10180,13 +10446,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="3"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0149"/>
     <x v="45"/>
     <s v="CLI-011"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="11200"/>
     <s v="USD"/>
@@ -10195,13 +10461,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0150"/>
     <x v="45"/>
     <s v="CLI-012"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="456"/>
     <s v="USD"/>
@@ -10210,13 +10476,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="9"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0151"/>
     <x v="46"/>
     <s v="CLI-007"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="1616"/>
     <s v="USD"/>
@@ -10225,13 +10491,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0152"/>
     <x v="46"/>
     <s v="CLI-017"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="2351"/>
     <s v="USD"/>
@@ -10240,13 +10506,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="6"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0153"/>
     <x v="46"/>
     <s v="CLI-007"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="9900"/>
     <s v="USD"/>
@@ -10255,13 +10521,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0154"/>
     <x v="47"/>
     <s v="CLI-001"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="18833"/>
     <s v="USD"/>
@@ -10270,13 +10536,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="0"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0155"/>
     <x v="47"/>
     <s v="CLI-010"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="8108"/>
     <s v="USD"/>
@@ -10285,13 +10551,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="4"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0156"/>
     <x v="48"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="903"/>
     <s v="USD"/>
@@ -10300,13 +10566,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0157"/>
     <x v="48"/>
     <s v="CLI-025"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="2442"/>
     <s v="USD"/>
@@ -10315,13 +10581,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="14"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0158"/>
     <x v="48"/>
     <s v="CLI-020"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="1174"/>
     <s v="USD"/>
@@ -10330,13 +10596,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="20"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0159"/>
     <x v="48"/>
     <s v="CLI-006"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="1078"/>
     <s v="USD"/>
@@ -10345,13 +10611,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="12"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0160"/>
     <x v="48"/>
     <s v="CLI-001"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="1366"/>
     <s v="USD"/>
@@ -10360,13 +10626,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="0"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0161"/>
     <x v="49"/>
     <s v="CLI-004"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="7756"/>
     <s v="USD"/>
@@ -10375,13 +10641,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="5"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0162"/>
     <x v="49"/>
     <s v="CLI-020"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="8610"/>
     <s v="USD"/>
@@ -10390,13 +10656,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="20"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0163"/>
     <x v="49"/>
     <s v="CLI-018"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="8111"/>
     <s v="USD"/>
@@ -10405,13 +10671,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="19"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0164"/>
     <x v="49"/>
     <s v="CLI-021"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="4705"/>
     <s v="USD"/>
@@ -10420,13 +10686,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="24"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0165"/>
     <x v="49"/>
     <s v="CLI-014"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="1372"/>
     <s v="USD"/>
@@ -10435,13 +10701,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="10"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0166"/>
     <x v="49"/>
     <s v="CLI-005"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="1962"/>
     <s v="USD"/>
@@ -10450,13 +10716,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="15"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0167"/>
     <x v="49"/>
     <s v="CLI-025"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="7472"/>
     <s v="USD"/>
@@ -10465,13 +10731,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="14"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0168"/>
     <x v="49"/>
     <s v="CLI-004"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="3263"/>
     <s v="USD"/>
@@ -10480,13 +10746,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="5"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0169"/>
     <x v="50"/>
     <s v="CLI-007"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="3766"/>
     <s v="USD"/>
@@ -10495,13 +10761,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0170"/>
     <x v="50"/>
     <s v="CLI-001"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="18881"/>
     <s v="USD"/>
@@ -10510,13 +10776,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="0"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0171"/>
     <x v="50"/>
     <s v="CLI-023"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="349"/>
     <s v="USD"/>
@@ -10525,13 +10791,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="13"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0172"/>
     <x v="50"/>
     <s v="CLI-006"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="5475"/>
     <s v="USD"/>
@@ -10540,13 +10806,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="12"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0173"/>
     <x v="51"/>
     <s v="CLI-022"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="3042"/>
     <s v="USD"/>
@@ -10555,13 +10821,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="8"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0174"/>
     <x v="51"/>
     <s v="CLI-003"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="4847"/>
     <s v="USD"/>
@@ -10570,13 +10836,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0175"/>
     <x v="51"/>
     <s v="CLI-019"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="17137"/>
     <s v="USD"/>
@@ -10585,13 +10851,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="3"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0176"/>
     <x v="51"/>
     <s v="CLI-016"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="6377"/>
     <s v="USD"/>
@@ -10600,13 +10866,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="1"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0177"/>
     <x v="52"/>
     <s v="CLI-025"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="290"/>
     <s v="USD"/>
@@ -10615,13 +10881,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="14"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0178"/>
     <x v="52"/>
     <s v="CLI-006"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="4076"/>
     <s v="USD"/>
@@ -10630,13 +10896,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="12"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0179"/>
     <x v="53"/>
     <s v="CLI-001"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="8060"/>
     <s v="USD"/>
@@ -10645,13 +10911,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="0"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0180"/>
     <x v="53"/>
     <s v="CLI-007"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="9205"/>
     <s v="USD"/>
@@ -10660,13 +10926,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0181"/>
     <x v="53"/>
     <s v="CLI-017"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="2591"/>
     <s v="USD"/>
@@ -10675,13 +10941,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="6"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0182"/>
     <x v="53"/>
     <s v="CLI-020"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="3199"/>
     <s v="USD"/>
@@ -10690,13 +10956,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="20"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0183"/>
     <x v="53"/>
     <s v="CLI-003"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="5023"/>
     <s v="USD"/>
@@ -10705,13 +10971,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0184"/>
     <x v="54"/>
     <s v="CLI-013"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="15900"/>
     <s v="USD"/>
@@ -10720,13 +10986,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="11"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0185"/>
     <x v="54"/>
     <s v="CLI-002"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="4405"/>
     <s v="USD"/>
@@ -10735,13 +11001,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="2"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0186"/>
     <x v="54"/>
     <s v="CLI-002"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="2865"/>
     <s v="USD"/>
@@ -10750,13 +11016,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="2"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0187"/>
     <x v="54"/>
     <s v="CLI-010"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="10987"/>
     <s v="USD"/>
@@ -10765,13 +11031,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="4"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0188"/>
     <x v="55"/>
     <s v="CLI-014"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="4599"/>
     <s v="USD"/>
@@ -10780,13 +11046,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="10"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0189"/>
     <x v="55"/>
     <s v="CLI-017"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="16799"/>
     <s v="USD"/>
@@ -10795,13 +11061,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="6"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0190"/>
     <x v="55"/>
     <s v="CLI-010"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="6052"/>
     <s v="USD"/>
@@ -10810,13 +11076,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="4"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0191"/>
     <x v="55"/>
     <s v="CLI-011"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="8820"/>
     <s v="USD"/>
@@ -10825,13 +11091,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0192"/>
     <x v="56"/>
     <s v="CLI-011"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="10809"/>
     <s v="USD"/>
@@ -10840,13 +11106,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0193"/>
     <x v="57"/>
     <s v="CLI-022"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="537"/>
     <s v="USD"/>
@@ -10855,13 +11121,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="8"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0194"/>
     <x v="58"/>
     <s v="CLI-018"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="22346"/>
     <s v="USD"/>
@@ -10870,13 +11136,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="19"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0195"/>
     <x v="59"/>
     <s v="CLI-012"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="1401"/>
     <s v="USD"/>
@@ -10885,13 +11151,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="9"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0196"/>
     <x v="59"/>
     <s v="CLI-023"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="1424"/>
     <s v="USD"/>
@@ -10900,13 +11166,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="13"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0197"/>
     <x v="59"/>
     <s v="CLI-024"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="1910"/>
     <s v="USD"/>
@@ -10915,13 +11181,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="23"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0198"/>
     <x v="59"/>
     <s v="CLI-025"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="6777"/>
     <s v="USD"/>
@@ -10930,13 +11196,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="14"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0199"/>
     <x v="60"/>
     <s v="CLI-012"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="604"/>
     <s v="USD"/>
@@ -10945,13 +11211,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="9"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0200"/>
     <x v="60"/>
     <s v="CLI-012"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="1696"/>
     <s v="USD"/>
@@ -10960,13 +11226,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="9"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0201"/>
     <x v="60"/>
     <s v="CLI-021"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="9040"/>
     <s v="USD"/>
@@ -10975,13 +11241,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="24"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0202"/>
     <x v="61"/>
     <s v="CLI-002"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="583"/>
     <s v="USD"/>
@@ -10990,13 +11256,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="2"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0203"/>
     <x v="61"/>
     <s v="CLI-002"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="10701"/>
     <s v="USD"/>
@@ -11005,13 +11271,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="2"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0204"/>
     <x v="61"/>
     <s v="CLI-013"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="5830"/>
     <s v="USD"/>
@@ -11020,13 +11286,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="11"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0205"/>
     <x v="62"/>
     <s v="CLI-017"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="21669"/>
     <s v="USD"/>
@@ -11035,13 +11301,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="6"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0206"/>
     <x v="62"/>
     <s v="CLI-016"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="1869"/>
     <s v="USD"/>
@@ -11050,13 +11316,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="1"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0207"/>
     <x v="63"/>
     <s v="CLI-014"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="938"/>
     <s v="USD"/>
@@ -11065,13 +11331,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="10"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0208"/>
     <x v="63"/>
     <s v="CLI-010"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="1560"/>
     <s v="USD"/>
@@ -11080,13 +11346,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="4"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0209"/>
     <x v="63"/>
     <s v="CLI-023"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="759"/>
     <s v="USD"/>
@@ -11095,13 +11361,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="13"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0210"/>
     <x v="63"/>
     <s v="CLI-018"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="2389"/>
     <s v="USD"/>
@@ -11110,13 +11376,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="19"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0211"/>
     <x v="63"/>
     <s v="CLI-015"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="7393"/>
     <s v="USD"/>
@@ -11125,13 +11391,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="18"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0212"/>
     <x v="63"/>
     <s v="CLI-021"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="500"/>
     <s v="USD"/>
@@ -11140,13 +11406,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="24"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0213"/>
     <x v="63"/>
     <s v="CLI-013"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="4929"/>
     <s v="USD"/>
@@ -11155,13 +11421,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="11"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0214"/>
     <x v="64"/>
     <s v="CLI-004"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="5502"/>
     <s v="USD"/>
@@ -11170,13 +11436,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="5"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0215"/>
     <x v="64"/>
     <s v="CLI-025"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="23630"/>
     <s v="USD"/>
@@ -11185,13 +11451,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="14"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0216"/>
     <x v="64"/>
     <s v="CLI-003"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="18167"/>
     <s v="USD"/>
@@ -11200,13 +11466,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0217"/>
     <x v="64"/>
     <s v="CLI-014"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="878"/>
     <s v="USD"/>
@@ -11215,13 +11481,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="10"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0218"/>
     <x v="65"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="4671"/>
     <s v="USD"/>
@@ -11230,13 +11496,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0219"/>
     <x v="66"/>
     <s v="CLI-014"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="1609"/>
     <s v="USD"/>
@@ -11245,13 +11511,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="10"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0220"/>
     <x v="66"/>
     <s v="CLI-024"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="8189"/>
     <s v="USD"/>
@@ -11260,13 +11526,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="23"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0221"/>
     <x v="66"/>
     <s v="CLI-023"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="185"/>
     <s v="USD"/>
@@ -11275,13 +11541,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="13"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0222"/>
     <x v="66"/>
     <s v="CLI-005"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="7341"/>
     <s v="USD"/>
@@ -11290,13 +11556,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="15"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0223"/>
     <x v="66"/>
     <s v="CLI-004"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="2128"/>
     <s v="USD"/>
@@ -11305,13 +11571,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="5"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0224"/>
     <x v="66"/>
     <s v="CLI-025"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="678"/>
     <s v="USD"/>
@@ -11320,13 +11586,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="14"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0225"/>
     <x v="66"/>
     <s v="CLI-005"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="2612"/>
     <s v="USD"/>
@@ -11335,13 +11601,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="15"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0226"/>
     <x v="66"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="254"/>
     <s v="USD"/>
@@ -11350,13 +11616,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0227"/>
     <x v="67"/>
     <s v="CLI-015"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="23432"/>
     <s v="USD"/>
@@ -11365,13 +11631,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="18"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0228"/>
     <x v="67"/>
     <s v="CLI-018"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="2421"/>
     <s v="USD"/>
@@ -11380,13 +11646,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="19"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0229"/>
     <x v="67"/>
     <s v="CLI-022"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="4651"/>
     <s v="USD"/>
@@ -11395,13 +11661,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="8"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0230"/>
     <x v="67"/>
     <s v="CLI-019"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="20751"/>
     <s v="USD"/>
@@ -11410,13 +11676,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="3"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0231"/>
     <x v="67"/>
     <s v="CLI-005"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="929"/>
     <s v="USD"/>
@@ -11425,13 +11691,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="15"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0232"/>
     <x v="67"/>
     <s v="CLI-008"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="283"/>
     <s v="USD"/>
@@ -11440,13 +11706,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="21"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0233"/>
     <x v="68"/>
     <s v="CLI-020"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="1839"/>
     <s v="USD"/>
@@ -11455,13 +11721,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="20"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0234"/>
     <x v="68"/>
     <s v="CLI-015"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="1704"/>
     <s v="USD"/>
@@ -11470,13 +11736,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="18"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0235"/>
     <x v="68"/>
     <s v="CLI-017"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="6883"/>
     <s v="USD"/>
@@ -11485,13 +11751,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="6"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0236"/>
     <x v="69"/>
     <s v="CLI-014"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="3610"/>
     <s v="USD"/>
@@ -11500,13 +11766,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="10"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0237"/>
     <x v="69"/>
     <s v="CLI-016"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="20977"/>
     <s v="USD"/>
@@ -11515,13 +11781,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="1"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0238"/>
     <x v="69"/>
     <s v="CLI-014"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="12097"/>
     <s v="USD"/>
@@ -11530,13 +11796,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="10"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0239"/>
     <x v="69"/>
     <s v="CLI-008"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="2473"/>
     <s v="USD"/>
@@ -11545,13 +11811,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="21"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0240"/>
     <x v="69"/>
     <s v="CLI-010"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="8845"/>
     <s v="USD"/>
@@ -11560,13 +11826,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="4"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0241"/>
     <x v="69"/>
     <s v="CLI-024"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="1177"/>
     <s v="USD"/>
@@ -11575,13 +11841,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="23"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0242"/>
     <x v="69"/>
     <s v="CLI-005"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="10728"/>
     <s v="USD"/>
@@ -11590,13 +11856,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="15"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0243"/>
     <x v="70"/>
     <s v="CLI-019"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="21413"/>
     <s v="USD"/>
@@ -11605,13 +11871,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="3"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0244"/>
     <x v="70"/>
     <s v="CLI-010"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="603"/>
     <s v="USD"/>
@@ -11620,13 +11886,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="4"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0245"/>
     <x v="71"/>
     <s v="CLI-019"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="10846"/>
     <s v="USD"/>
@@ -11635,13 +11901,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="3"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0246"/>
     <x v="71"/>
     <s v="CLI-005"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="1619"/>
     <s v="USD"/>
@@ -11650,13 +11916,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="15"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0247"/>
     <x v="71"/>
     <s v="CLI-013"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="17483"/>
     <s v="USD"/>
@@ -11665,13 +11931,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="11"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0248"/>
     <x v="71"/>
     <s v="CLI-007"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="6424"/>
     <s v="USD"/>
@@ -11680,13 +11946,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0249"/>
     <x v="72"/>
     <s v="CLI-007"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="1290"/>
     <s v="USD"/>
@@ -11695,13 +11961,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0250"/>
     <x v="72"/>
     <s v="CLI-010"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="2596"/>
     <s v="USD"/>
@@ -11710,13 +11976,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="4"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0251"/>
     <x v="72"/>
     <s v="CLI-005"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="1310"/>
     <s v="USD"/>
@@ -11725,13 +11991,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="15"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0252"/>
     <x v="72"/>
     <s v="CLI-025"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="21562"/>
     <s v="USD"/>
@@ -11740,13 +12006,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="14"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0253"/>
     <x v="72"/>
     <s v="CLI-008"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="6504"/>
     <s v="USD"/>
@@ -11755,13 +12021,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="21"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0254"/>
     <x v="73"/>
     <s v="CLI-010"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="3371"/>
     <s v="USD"/>
@@ -11770,13 +12036,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="4"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0255"/>
     <x v="73"/>
     <s v="CLI-020"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="1557"/>
     <s v="USD"/>
@@ -11785,13 +12051,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="20"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0256"/>
     <x v="73"/>
     <s v="CLI-014"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="1780"/>
     <s v="USD"/>
@@ -11800,13 +12066,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="10"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0257"/>
     <x v="74"/>
     <s v="CLI-016"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="1917"/>
     <s v="USD"/>
@@ -11815,13 +12081,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="1"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0258"/>
     <x v="74"/>
     <s v="CLI-017"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="4869"/>
     <s v="USD"/>
@@ -11830,13 +12096,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="6"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0259"/>
     <x v="74"/>
     <s v="CLI-015"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="4682"/>
     <s v="USD"/>
@@ -11845,13 +12111,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="18"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0260"/>
     <x v="74"/>
     <s v="CLI-018"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="1977"/>
     <s v="USD"/>
@@ -11860,13 +12126,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="19"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0261"/>
     <x v="74"/>
     <s v="CLI-020"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="10676"/>
     <s v="USD"/>
@@ -11875,13 +12141,13 @@
     <s v="Saltmarsh Foods"/>
     <s v="Ireland"/>
     <x v="20"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0262"/>
     <x v="75"/>
     <s v="CLI-004"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="792"/>
     <s v="USD"/>
@@ -11890,13 +12156,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="5"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0263"/>
     <x v="75"/>
     <s v="CLI-020"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="1818"/>
     <s v="USD"/>
@@ -11905,13 +12171,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="20"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0264"/>
     <x v="75"/>
     <s v="CLI-021"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="12574"/>
     <s v="USD"/>
@@ -11920,13 +12186,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="24"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0265"/>
     <x v="76"/>
     <s v="CLI-008"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="3238"/>
     <s v="USD"/>
@@ -11935,13 +12201,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="21"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0266"/>
     <x v="77"/>
     <s v="CLI-002"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="8182"/>
     <s v="USD"/>
@@ -11950,13 +12216,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="2"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0267"/>
     <x v="77"/>
     <s v="CLI-012"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="17144"/>
     <s v="USD"/>
@@ -11965,13 +12231,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="9"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0268"/>
     <x v="77"/>
     <s v="CLI-015"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Credit"/>
     <n v="12777"/>
     <s v="USD"/>
@@ -11980,13 +12246,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="18"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0269"/>
     <x v="78"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="689"/>
     <s v="USD"/>
@@ -11995,13 +12261,13 @@
     <s v="Baytown Supply Co"/>
     <s v="United States"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0270"/>
     <x v="78"/>
     <s v="CLI-002"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="1853"/>
     <s v="USD"/>
@@ -12010,13 +12276,13 @@
     <s v="Meridian Packaging"/>
     <s v="Canada"/>
     <x v="2"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0271"/>
     <x v="78"/>
     <s v="CLI-023"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="2389"/>
     <s v="USD"/>
@@ -12025,13 +12291,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="13"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0272"/>
     <x v="79"/>
     <s v="CLI-021"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="6013"/>
     <s v="USD"/>
@@ -12040,13 +12306,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="24"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0273"/>
     <x v="79"/>
     <s v="CLI-001"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="16373"/>
     <s v="USD"/>
@@ -12055,13 +12321,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="0"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0274"/>
     <x v="79"/>
     <s v="CLI-005"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="2037"/>
     <s v="USD"/>
@@ -12070,13 +12336,13 @@
     <s v="Norvale Trading Ltd"/>
     <s v="Cyprus"/>
     <x v="15"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0275"/>
     <x v="80"/>
     <s v="CLI-025"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="5056"/>
     <s v="USD"/>
@@ -12085,13 +12351,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="14"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0276"/>
     <x v="80"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="760"/>
     <s v="USD"/>
@@ -12100,13 +12366,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0277"/>
     <x v="80"/>
     <s v="CLI-024"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="4980"/>
     <s v="USD"/>
@@ -12115,13 +12381,13 @@
     <s v="Quintal Shipping"/>
     <s v="Panama"/>
     <x v="23"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0278"/>
     <x v="81"/>
     <s v="CLI-011"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="10546"/>
     <s v="USD"/>
@@ -12130,13 +12396,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0279"/>
     <x v="81"/>
     <s v="CLI-011"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="1765"/>
     <s v="USD"/>
@@ -12145,13 +12411,13 @@
     <s v="Petra Energy Partners"/>
     <s v="United States"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0280"/>
     <x v="82"/>
     <s v="CLI-001"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="15899"/>
     <s v="USD"/>
@@ -12160,13 +12426,13 @@
     <s v="Alpine Freight Services"/>
     <s v="Canada"/>
     <x v="0"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0281"/>
     <x v="82"/>
     <s v="CLI-025"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="6378"/>
     <s v="USD"/>
@@ -12175,13 +12441,13 @@
     <s v="Delta Ridge Partners"/>
     <s v="United States"/>
     <x v="14"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0282"/>
     <x v="82"/>
     <s v="CLI-009"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Credit"/>
     <n v="7791"/>
     <s v="USD"/>
@@ -12190,13 +12456,13 @@
     <s v="Grandview Logistics"/>
     <s v="Mexico"/>
     <x v="7"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0283"/>
     <x v="82"/>
     <s v="CLI-018"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="21010"/>
     <s v="USD"/>
@@ -12205,13 +12471,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="19"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0284"/>
     <x v="82"/>
     <s v="CLI-006"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="1311"/>
     <s v="USD"/>
@@ -12220,13 +12486,13 @@
     <s v="Kelso Agricultural"/>
     <s v="Australia"/>
     <x v="12"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0285"/>
     <x v="82"/>
     <s v="CLI-024"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="125"/>
     <s v="USD"/>
@@ -12235,13 +12501,13 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="23"/>
-    <s v="High"/>
+    <x v="2"/>
   </r>
   <r>
     <s v="TX0286"/>
     <x v="82"/>
     <s v="CLI-013"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="11807"/>
     <s v="USD"/>
@@ -12250,13 +12516,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="11"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0287"/>
     <x v="83"/>
     <s v="CLI-003"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="109"/>
     <s v="USD"/>
@@ -12265,13 +12531,13 @@
     <s v="Eastbrook Media"/>
     <s v="United Kingdom"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0288"/>
     <x v="83"/>
     <s v="CLI-003"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="3110"/>
     <s v="USD"/>
@@ -12280,13 +12546,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="16"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0289"/>
     <x v="83"/>
     <s v="CLI-023"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="2106"/>
     <s v="USD"/>
@@ -12295,13 +12561,13 @@
     <s v="Torrent Data Systems"/>
     <s v="United States"/>
     <x v="13"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0290"/>
     <x v="84"/>
     <s v="CLI-013"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Credit"/>
     <n v="6642"/>
     <s v="USD"/>
@@ -12310,13 +12576,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="11"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0291"/>
     <x v="84"/>
     <s v="CLI-013"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="8291"/>
     <s v="USD"/>
@@ -12325,13 +12591,13 @@
     <s v="Oakfield Components"/>
     <s v="Ireland"/>
     <x v="11"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0292"/>
     <x v="84"/>
     <s v="CLI-002"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Debit"/>
     <n v="1731"/>
     <s v="USD"/>
@@ -12340,13 +12606,13 @@
     <s v="Riverton Textiles"/>
     <s v="Mexico"/>
     <x v="2"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0293"/>
     <x v="85"/>
     <s v="CLI-011"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Debit"/>
     <n v="2401"/>
     <s v="USD"/>
@@ -12355,13 +12621,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="17"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0294"/>
     <x v="85"/>
     <s v="CLI-006"/>
-    <s v="Wire"/>
+    <x v="0"/>
     <s v="Credit"/>
     <n v="83"/>
     <s v="USD"/>
@@ -12370,13 +12636,13 @@
     <s v="Ferrum Steel Works"/>
     <s v="Germany"/>
     <x v="12"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0295"/>
     <x v="85"/>
     <s v="CLI-007"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="2238"/>
     <s v="USD"/>
@@ -12385,13 +12651,13 @@
     <s v="Halcyon Marine"/>
     <s v="Singapore"/>
     <x v="22"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0296"/>
     <x v="85"/>
     <s v="CLI-015"/>
-    <s v="Card"/>
+    <x v="3"/>
     <s v="Debit"/>
     <n v="1301"/>
     <s v="USD"/>
@@ -12400,13 +12666,13 @@
     <s v="Inverness Tooling"/>
     <s v="United Kingdom"/>
     <x v="18"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0297"/>
     <x v="85"/>
     <s v="CLI-013"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="4187"/>
     <s v="USD"/>
@@ -12415,13 +12681,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="11"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0298"/>
     <x v="86"/>
     <s v="CLI-022"/>
-    <s v="Check"/>
+    <x v="1"/>
     <s v="Credit"/>
     <n v="10917"/>
     <s v="USD"/>
@@ -12430,13 +12696,13 @@
     <s v="Corvus Metals"/>
     <s v="Germany"/>
     <x v="8"/>
-    <s v="Medium"/>
+    <x v="1"/>
   </r>
   <r>
     <s v="TX0299"/>
     <x v="87"/>
     <s v="CLI-023"/>
-    <s v="ACH"/>
+    <x v="4"/>
     <s v="Debit"/>
     <n v="3884"/>
     <s v="USD"/>
@@ -12445,13 +12711,13 @@
     <s v="Jadewater Trading"/>
     <s v="Singapore"/>
     <x v="13"/>
-    <s v="Low"/>
+    <x v="0"/>
   </r>
   <r>
     <s v="TX0300"/>
     <x v="87"/>
     <s v="CLI-019"/>
-    <s v="Cash"/>
+    <x v="2"/>
     <s v="Debit"/>
     <n v="16333"/>
     <s v="USD"/>
@@ -12460,13 +12726,778 @@
     <s v="Larkspur Consulting"/>
     <s v="United States"/>
     <x v="3"/>
+    <x v="1"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="40">
+  <r>
+    <s v="ENG-1001"/>
+    <s v="CLI-001"/>
+    <s v="Year-End Audit"/>
+    <x v="0"/>
+    <s v="S. Bhatt"/>
+    <d v="2026-02-08T00:00:00"/>
+    <d v="2026-08-17T00:00:00"/>
+    <n v="478500"/>
+    <n v="358900"/>
+    <x v="0"/>
+    <n v="119600"/>
+    <n v="0.24994775339602926"/>
+    <n v="514387.5"/>
+    <s v="Aldridge Manufacturing"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1002"/>
+    <s v="CLI-004"/>
+    <s v="Transfer Pricing Review"/>
+    <x v="1"/>
+    <s v="U. Castellanos"/>
+    <d v="2026-03-11T00:00:00"/>
+    <d v="2026-05-25T00:00:00"/>
+    <n v="298500"/>
+    <n v="364200"/>
+    <x v="0"/>
+    <n v="-65700"/>
+    <n v="-0.2201005025125628"/>
+    <n v="320887.5"/>
+    <s v="Dunmore Energy"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1003"/>
+    <s v="CLI-007"/>
+    <s v="Controls Assessment"/>
+    <x v="2"/>
+    <s v="W. Achebe"/>
+    <d v="2026-05-05T00:00:00"/>
+    <d v="2026-09-24T00:00:00"/>
+    <n v="448500"/>
+    <n v="408100"/>
+    <x v="0"/>
+    <n v="40400"/>
+    <n v="9.0078037904124858E-2"/>
+    <n v="482137.5"/>
+    <s v="Granite Peak Mining"/>
     <s v="Medium"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1004"/>
+    <s v="CLI-010"/>
+    <s v="AML Programme Review"/>
+    <x v="3"/>
+    <s v="T. Nakamura"/>
+    <d v="2026-01-29T00:00:00"/>
+    <d v="2026-07-17T00:00:00"/>
+    <n v="59500"/>
+    <m/>
+    <x v="1"/>
+    <s v="NO COST YET"/>
+    <s v="NO COST YET"/>
+    <n v="63962.5"/>
+    <s v="Juniper Health Systems"/>
+    <s v="Medium"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1005"/>
+    <s v="CLI-013"/>
+    <s v="Cost Optimisation"/>
+    <x v="4"/>
+    <s v="V. Ostrowski"/>
+    <d v="2026-04-25T00:00:00"/>
+    <d v="2026-11-11T00:00:00"/>
+    <n v="435000"/>
+    <n v="295800"/>
+    <x v="2"/>
+    <n v="139200"/>
+    <n v="0.32"/>
+    <n v="467625"/>
+    <s v="Mosaic Holdings"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1006"/>
+    <s v="CLI-016"/>
+    <s v="Vendor Risk Review"/>
+    <x v="0"/>
+    <s v="S. Bhatt"/>
+    <d v="2026-04-29T00:00:00"/>
+    <d v="2026-08-20T00:00:00"/>
+    <n v="414000"/>
+    <n v="376700"/>
+    <x v="3"/>
+    <n v="37300"/>
+    <n v="9.0096618357487918E-2"/>
+    <n v="445050"/>
+    <s v="Pinehurst Capital"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1007"/>
+    <s v="CLI-019"/>
+    <s v="Statutory Reporting"/>
+    <x v="1"/>
+    <s v="U. Castellanos"/>
+    <d v="2026-01-31T00:00:00"/>
+    <d v="2026-06-06T00:00:00"/>
+    <n v="60500"/>
+    <n v="41100"/>
+    <x v="0"/>
+    <n v="19400"/>
+    <n v="0.32066115702479336"/>
+    <n v="65037.5"/>
+    <s v="Silverbrook Bank"/>
+    <s v="Medium"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1008"/>
+    <s v="CLI-022"/>
+    <s v="Due Diligence"/>
+    <x v="2"/>
+    <s v="W. Achebe"/>
+    <d v="2026-01-11T00:00:00"/>
+    <d v="2026-07-13T00:00:00"/>
+    <n v="49500"/>
+    <n v="54900"/>
+    <x v="0"/>
+    <n v="-5400"/>
+    <n v="-0.10909090909090909"/>
+    <n v="53212.5"/>
+    <s v="Vanguard Rail"/>
+    <s v="Medium"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1009"/>
+    <s v="CLI-025"/>
+    <s v="Payroll Assurance"/>
+    <x v="3"/>
+    <s v="T. Nakamura"/>
+    <d v="2026-03-01T00:00:00"/>
+    <d v="2026-08-01T00:00:00"/>
+    <n v="416500"/>
+    <n v="283200"/>
+    <x v="0"/>
+    <n v="133300"/>
+    <n v="0.32004801920768305"/>
+    <n v="447737.5"/>
+    <s v="Zephyr Telecom"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1010"/>
+    <s v="CLI-003"/>
+    <s v="Data Migration Assurance"/>
+    <x v="4"/>
+    <s v="V. Ostrowski"/>
+    <d v="2026-05-20T00:00:00"/>
+    <d v="2026-08-29T00:00:00"/>
+    <n v="436000"/>
+    <m/>
+    <x v="1"/>
+    <s v="NO COST YET"/>
+    <s v="NO COST YET"/>
+    <n v="468700"/>
+    <s v="Cardinal Freight"/>
+    <s v="Medium"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1011"/>
+    <s v="CLI-006"/>
+    <s v="Year-End Audit"/>
+    <x v="0"/>
+    <s v="S. Bhatt"/>
+    <d v="2026-05-11T00:00:00"/>
+    <d v="2026-11-13T00:00:00"/>
+    <n v="164000"/>
+    <n v="170600"/>
+    <x v="2"/>
+    <n v="-6600"/>
+    <n v="-4.0243902439024391E-2"/>
+    <n v="176300"/>
+    <s v="Fairmont Retail Group"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1012"/>
+    <s v="CLI-099"/>
+    <s v="Transfer Pricing Review"/>
+    <x v="1"/>
+    <s v="U. Castellanos"/>
+    <d v="2026-03-05T00:00:00"/>
+    <d v="2026-06-14T00:00:00"/>
+    <n v="434500"/>
+    <n v="530100"/>
+    <x v="3"/>
+    <n v="-95600"/>
+    <n v="-0.22002301495972382"/>
+    <n v="467087.5"/>
+    <s v="CHECK CLIENT ID"/>
+    <s v="No Risk Rating"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1013"/>
+    <s v="CLI-012"/>
+    <s v="Controls Assessment"/>
+    <x v="2"/>
+    <s v="W. Achebe"/>
+    <d v="2026-03-20T00:00:00"/>
+    <d v="2026-05-09T00:00:00"/>
+    <n v="258000"/>
+    <n v="193500"/>
+    <x v="0"/>
+    <n v="64500"/>
+    <n v="0.25"/>
+    <n v="277350"/>
+    <s v="Lakeshore Utilities"/>
+    <s v="High"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1014"/>
+    <s v="CLI-015"/>
+    <s v="AML Programme Review"/>
+    <x v="3"/>
+    <s v="T. Nakamura"/>
+    <d v="2026-02-21T00:00:00"/>
+    <d v="2026-09-15T00:00:00"/>
+    <n v="415500"/>
+    <n v="403000"/>
+    <x v="0"/>
+    <n v="12500"/>
+    <n v="3.0084235860409144E-2"/>
+    <n v="446662.5"/>
+    <s v="Orchard Bay Hotels"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1015"/>
+    <s v="CLI-018"/>
+    <s v="Cost Optimisation"/>
+    <x v="4"/>
+    <s v="V. Ostrowski"/>
+    <d v="2026-02-04T00:00:00"/>
+    <d v="2026-06-14T00:00:00"/>
+    <n v="414000"/>
+    <n v="459500"/>
+    <x v="0"/>
+    <n v="-45500"/>
+    <n v="-0.10990338164251208"/>
+    <n v="445050"/>
+    <s v="Redstone Media"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1016"/>
+    <s v="CLI-021"/>
+    <s v="Vendor Risk Review"/>
+    <x v="0"/>
+    <s v="S. Bhatt"/>
+    <d v="2026-05-14T00:00:00"/>
+    <d v="2026-08-15T00:00:00"/>
+    <n v="200000"/>
+    <n v="194000"/>
+    <x v="1"/>
+    <n v="6000"/>
+    <n v="0.03"/>
+    <n v="215000"/>
+    <s v="Umberton Textiles"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1017"/>
+    <s v="CLI-024"/>
+    <s v="Statutory Reporting"/>
+    <x v="1"/>
+    <s v="U. Castellanos"/>
+    <d v="2026-05-12T00:00:00"/>
+    <d v="2026-11-02T00:00:00"/>
+    <n v="246000"/>
+    <n v="167300"/>
+    <x v="2"/>
+    <n v="78700"/>
+    <n v="0.3199186991869919"/>
+    <n v="264450"/>
+    <s v="Yarrow Biotech"/>
+    <s v="High"/>
+    <n v="2"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1018"/>
+    <s v="CLI-002"/>
+    <s v="Due Diligence"/>
+    <x v="2"/>
+    <s v="W. Achebe"/>
+    <d v="2026-05-07T00:00:00"/>
+    <d v="2026-08-22T00:00:00"/>
+    <n v="425500"/>
+    <n v="472300"/>
+    <x v="3"/>
+    <n v="-46800"/>
+    <n v="-0.10998824911868391"/>
+    <n v="457412.5"/>
+    <s v="Bellhaven Foods"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1019"/>
+    <s v="CLI-005"/>
+    <s v="Payroll Assurance"/>
+    <x v="3"/>
+    <s v="T. Nakamura"/>
+    <d v="2026-04-21T00:00:00"/>
+    <d v="2026-07-19T00:00:00"/>
+    <n v="232500"/>
+    <m/>
+    <x v="0"/>
+    <s v="NO COST YET"/>
+    <s v="NO COST YET"/>
+    <n v="249937.5"/>
+    <s v="Eastvale Logistics"/>
+    <s v="High"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1020"/>
+    <s v="CLI-008"/>
+    <s v="Data Migration Assurance"/>
+    <x v="4"/>
+    <s v="V. Ostrowski"/>
+    <d v="2026-01-27T00:00:00"/>
+    <d v="2026-07-03T00:00:00"/>
+    <n v="384500"/>
+    <n v="288400"/>
+    <x v="0"/>
+    <n v="96100"/>
+    <n v="0.24993498049414825"/>
+    <n v="413337.5"/>
+    <s v="Harbour Line Shipping"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1021"/>
+    <s v="CLI-011"/>
+    <s v="Year-End Audit"/>
+    <x v="0"/>
+    <s v="S. Bhatt"/>
+    <d v="2026-02-15T00:00:00"/>
+    <d v="2026-08-12T00:00:00"/>
+    <n v="475000"/>
+    <n v="527200"/>
+    <x v="0"/>
+    <n v="-52200"/>
+    <n v="-0.10989473684210527"/>
+    <n v="510625"/>
+    <s v="Kestrel Aviation"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1022"/>
+    <s v="CLI-014"/>
+    <s v="Transfer Pricing Review"/>
+    <x v="1"/>
+    <s v="U. Castellanos"/>
+    <d v="2026-04-09T00:00:00"/>
+    <d v="2026-09-26T00:00:00"/>
+    <n v="420000"/>
+    <n v="285600"/>
+    <x v="1"/>
+    <n v="134400"/>
+    <n v="0.32"/>
+    <n v="451500"/>
+    <s v="Northgate Insurance"/>
+    <s v="Medium"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1023"/>
+    <s v="CLI-017"/>
+    <s v="Controls Assessment"/>
+    <x v="2"/>
+    <s v="W. Achebe"/>
+    <d v="2026-05-05T00:00:00"/>
+    <d v="2026-06-30T00:00:00"/>
+    <n v="202500"/>
+    <n v="224800"/>
+    <x v="2"/>
+    <n v="-22300"/>
+    <n v="-0.11012345679012346"/>
+    <n v="217687.5"/>
+    <s v="Quarry Ridge Cement"/>
+    <s v="High"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1024"/>
+    <s v="CLI-020"/>
+    <s v="AML Programme Review"/>
+    <x v="3"/>
+    <s v="T. Nakamura"/>
+    <d v="2026-02-17T00:00:00"/>
+    <d v="2026-05-16T00:00:00"/>
+    <n v="302000"/>
+    <n v="274800"/>
+    <x v="3"/>
+    <n v="27200"/>
+    <n v="9.006622516556291E-2"/>
+    <n v="324650"/>
+    <s v="Thornfield Chemicals"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1025"/>
+    <s v="CLI-023"/>
+    <s v="Cost Optimisation"/>
+    <x v="4"/>
+    <s v="V. Ostrowski"/>
+    <d v="2026-01-08T00:00:00"/>
+    <d v="2026-04-14T00:00:00"/>
+    <n v="321000"/>
+    <n v="292100"/>
+    <x v="0"/>
+    <n v="28900"/>
+    <n v="9.003115264797508E-2"/>
+    <n v="345075"/>
+    <s v="Westmere Property"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-104"/>
+    <s v="CLI-001"/>
+    <s v="Vendor Risk Review"/>
+    <x v="0"/>
+    <s v="S. Bhatt"/>
+    <d v="2026-04-18T00:00:00"/>
+    <d v="2026-10-11T00:00:00"/>
+    <n v="221000"/>
+    <n v="229800"/>
+    <x v="0"/>
+    <n v="-8800"/>
+    <n v="-3.9819004524886875E-2"/>
+    <n v="237575"/>
+    <s v="Aldridge Manufacturing"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="CHECK LENGTH"/>
+  </r>
+  <r>
+    <s v="ENG-1027"/>
+    <s v="CLI-004"/>
+    <s v="Statutory Reporting"/>
+    <x v="1"/>
+    <s v="U. Castellanos"/>
+    <d v="2026-05-02T00:00:00"/>
+    <d v="2026-08-23T00:00:00"/>
+    <n v="382500"/>
+    <n v="260100"/>
+    <x v="0"/>
+    <n v="122400"/>
+    <n v="0.32"/>
+    <n v="411187.5"/>
+    <s v="Dunmore Energy"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1028"/>
+    <s v="CLI-007"/>
+    <s v="Due Diligence"/>
+    <x v="2"/>
+    <s v="W. Achebe"/>
+    <d v="2026-04-13T00:00:00"/>
+    <d v="2026-10-06T00:00:00"/>
+    <n v="459000"/>
+    <m/>
+    <x v="1"/>
+    <s v="NO COST YET"/>
+    <s v="NO COST YET"/>
+    <n v="493425"/>
+    <s v="Granite Peak Mining"/>
+    <s v="Medium"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1029"/>
+    <s v="CLI-010"/>
+    <s v="Payroll Assurance"/>
+    <x v="3"/>
+    <s v="T. Nakamura"/>
+    <d v="2026-05-17T00:00:00"/>
+    <d v="2026-11-21T00:00:00"/>
+    <n v="150000"/>
+    <n v="166500"/>
+    <x v="2"/>
+    <n v="-16500"/>
+    <n v="-0.11"/>
+    <n v="161250"/>
+    <s v="Juniper Health Systems"/>
+    <s v="Medium"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1030"/>
+    <s v="CLI-013"/>
+    <s v="Data Migration Assurance"/>
+    <x v="4"/>
+    <s v="V. Ostrowski"/>
+    <d v="2026-01-19T00:00:00"/>
+    <d v="2026-07-06T00:00:00"/>
+    <n v="231500"/>
+    <n v="210700"/>
+    <x v="3"/>
+    <n v="20800"/>
+    <n v="8.9848812095032399E-2"/>
+    <n v="248862.5"/>
+    <s v="Mosaic Holdings"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1031"/>
+    <s v="CLI-016"/>
+    <s v="Year-End Audit"/>
+    <x v="0"/>
+    <s v="S. Bhatt"/>
+    <d v="2026-05-14T00:00:00"/>
+    <d v="2026-10-11T00:00:00"/>
+    <n v="293000"/>
+    <n v="304700"/>
+    <x v="0"/>
+    <n v="-11700"/>
+    <n v="-3.9931740614334472E-2"/>
+    <n v="314975"/>
+    <s v="Pinehurst Capital"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1032"/>
+    <s v="CLI-019"/>
+    <s v="Transfer Pricing Review"/>
+    <x v="1"/>
+    <s v="U. Castellanos"/>
+    <d v="2026-04-21T00:00:00"/>
+    <d v="2026-09-01T00:00:00"/>
+    <n v="45500"/>
+    <n v="47300"/>
+    <x v="0"/>
+    <n v="-1800"/>
+    <n v="-3.9560439560439559E-2"/>
+    <n v="48912.5"/>
+    <s v="Silverbrook Bank"/>
+    <s v="Medium"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1017"/>
+    <s v="CLI-022"/>
+    <s v="Controls Assessment"/>
+    <x v="2"/>
+    <s v="W. Achebe"/>
+    <d v="2026-05-02T00:00:00"/>
+    <d v="2026-11-16T00:00:00"/>
+    <n v="59000"/>
+    <n v="53700"/>
+    <x v="0"/>
+    <n v="5300"/>
+    <n v="8.9830508474576271E-2"/>
+    <n v="63425"/>
+    <s v="Vanguard Rail"/>
+    <s v="Medium"/>
+    <n v="2"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1034"/>
+    <s v="CLI-025"/>
+    <s v="AML Programme Review"/>
+    <x v="3"/>
+    <s v="T. Nakamura"/>
+    <d v="2026-02-19T00:00:00"/>
+    <d v="2026-08-23T00:00:00"/>
+    <n v="344000"/>
+    <n v="282100"/>
+    <x v="1"/>
+    <n v="61900"/>
+    <n v="0.17994186046511629"/>
+    <n v="369800"/>
+    <s v="Zephyr Telecom"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1035"/>
+    <s v="CLI-003"/>
+    <s v="Cost Optimisation"/>
+    <x v="4"/>
+    <s v="V. Ostrowski"/>
+    <d v="2026-01-28T00:00:00"/>
+    <d v="2026-08-02T00:00:00"/>
+    <n v="453000"/>
+    <m/>
+    <x v="2"/>
+    <s v="NO COST YET"/>
+    <s v="NO COST YET"/>
+    <n v="486975"/>
+    <s v="Cardinal Freight"/>
+    <s v="Medium"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1036"/>
+    <s v="CLI-006"/>
+    <s v="Vendor Risk Review"/>
+    <x v="0"/>
+    <s v="S. Bhatt"/>
+    <d v="2026-01-13T00:00:00"/>
+    <d v="2026-03-17T00:00:00"/>
+    <n v="87500"/>
+    <n v="59500"/>
+    <x v="3"/>
+    <n v="28000"/>
+    <n v="0.32"/>
+    <n v="94062.5"/>
+    <s v="Fairmont Retail Group"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1037"/>
+    <s v="CLI-009"/>
+    <s v="Statutory Reporting"/>
+    <x v="1"/>
+    <s v="U. Castellanos"/>
+    <d v="2026-04-30T00:00:00"/>
+    <d v="2026-06-17T00:00:00"/>
+    <n v="431000"/>
+    <n v="418100"/>
+    <x v="0"/>
+    <n v="12900"/>
+    <n v="2.9930394431554524E-2"/>
+    <n v="463325"/>
+    <s v="Ironwood Pharma"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1038"/>
+    <s v="CLI-012"/>
+    <s v="Due Diligence"/>
+    <x v="2"/>
+    <s v="W. Achebe"/>
+    <d v="2026-03-09T00:00:00"/>
+    <d v="2026-06-30T00:00:00"/>
+    <n v="101000"/>
+    <n v="82800"/>
+    <x v="0"/>
+    <n v="18200"/>
+    <n v="0.18019801980198019"/>
+    <n v="108575"/>
+    <s v="Lakeshore Utilities"/>
+    <s v="High"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1039"/>
+    <s v="CLI-015"/>
+    <s v="Payroll Assurance"/>
+    <x v="3"/>
+    <s v="T. Nakamura"/>
+    <d v="2026-04-03T00:00:00"/>
+    <d v="2026-07-31T00:00:00"/>
+    <n v="80500"/>
+    <n v="66000"/>
+    <x v="0"/>
+    <n v="14500"/>
+    <n v="0.18012422360248448"/>
+    <n v="86537.5"/>
+    <s v="Orchard Bay Hotels"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
+  </r>
+  <r>
+    <s v="ENG-1040"/>
+    <s v="CLI-018"/>
+    <s v="Data Migration Assurance"/>
+    <x v="4"/>
+    <s v="V. Ostrowski"/>
+    <d v="2026-02-14T00:00:00"/>
+    <d v="2026-06-04T00:00:00"/>
+    <n v="315000"/>
+    <m/>
+    <x v="1"/>
+    <s v="NO COST YET"/>
+    <s v="NO COST YET"/>
+    <n v="338625"/>
+    <s v="Redstone Media"/>
+    <s v="Low"/>
+    <n v="1"/>
+    <s v="OK"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59642C17-F301-463E-A3B8-03E3DB676B75}" name="PivotTable1" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59642C17-F301-463E-A3B8-03E3DB676B75}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:I31" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="15">
     <pivotField showAll="0"/>
@@ -12564,7 +13595,16 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField dataField="1" numFmtId="4" showAll="0"/>
     <pivotField showAll="0"/>
@@ -12611,7 +13651,14 @@
         </pivotArea>
       </autoSortScope>
     </pivotField>
-    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField showAll="0">
       <items count="369">
         <item x="0"/>
@@ -13137,8 +14184,147 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0CEC319E-5383-4446-8916-A20239C47C72}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:D9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="17">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="2"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="3" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="3" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="9" hier="-1"/>
+  </pageFields>
+  <dataFields count="3">
+    <dataField name="Sum of budget" fld="7" baseField="0" baseItem="0" numFmtId="3"/>
+    <dataField name="Sum of actual_cost" fld="8" baseField="0" baseItem="0"/>
+    <dataField name="Sum of variance" fld="10" baseField="3" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_txn_type" xr10:uid="{460F952C-E7B0-40E1-BB75-C4EE20895EB4}" sourceName="txn_type">
+  <pivotTables>
+    <pivotTable tabId="10" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1617725013">
+      <items count="5">
+        <i x="4" s="1"/>
+        <i x="3" s="1"/>
+        <i x="2" s="1"/>
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_risk_rating" xr10:uid="{BEF92EF8-594B-48DD-B1A7-1892148AA934}" sourceName="risk_rating">
+  <pivotTables>
+    <pivotTable tabId="10" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="1617725013">
+      <items count="3">
+        <i x="2" s="1"/>
+        <i x="0" s="1"/>
+        <i x="1" s="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="txn_type" xr10:uid="{81429635-F5F1-4961-A03E-E7AAC3EE4EBB}" cache="Slicer_txn_type" caption="txn_type" rowHeight="241300"/>
+  <slicer name="risk_rating" xr10:uid="{488454F9-C670-4A1D-A401-ACF829196F44}" cache="Slicer_risk_rating" caption="risk_rating" rowHeight="241300"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{38627FB0-5145-4F3F-A59B-FE35EC51E85E}" name="tblEng01" displayName="tblEng01" ref="A1:M41" headerRowDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{38627FB0-5145-4F3F-A59B-FE35EC51E85E}" name="tblEng01" displayName="tblEng01" ref="A1:M41" headerRowDxfId="13">
   <autoFilter ref="A1:M41" xr:uid="{38627FB0-5145-4F3F-A59B-FE35EC51E85E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J41">
     <sortCondition ref="A1:A41"/>
@@ -13149,10 +14335,10 @@
     <tableColumn id="3" xr3:uid="{B8BB6B56-8344-499F-BAB4-84715457D6EF}" name="engagement_name"/>
     <tableColumn id="4" xr3:uid="{039EFC86-5137-4E51-91AE-860C7AF50C24}" name="service_line"/>
     <tableColumn id="5" xr3:uid="{6FF6A3D2-17A1-4FD9-AEAA-C1032E532018}" name="manager"/>
-    <tableColumn id="6" xr3:uid="{75A6260E-7674-4FE9-BA83-0D2F7F16F9B5}" name="start_date" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{BEA051CC-DB8F-401A-9BD4-F8DA896A9836}" name="end_date" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{A133F6EB-61F1-447E-9563-209E1FE38970}" name="budget" totalsRowFunction="sum" dataDxfId="11" dataCellStyle="Comma"/>
-    <tableColumn id="9" xr3:uid="{19614B11-9DC3-43E2-AC6B-5229754C7678}" name="actual_cost" dataDxfId="10" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{75A6260E-7674-4FE9-BA83-0D2F7F16F9B5}" name="start_date" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{BEA051CC-DB8F-401A-9BD4-F8DA896A9836}" name="end_date" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{A133F6EB-61F1-447E-9563-209E1FE38970}" name="budget" totalsRowFunction="sum" dataDxfId="10" dataCellStyle="Comma"/>
+    <tableColumn id="9" xr3:uid="{19614B11-9DC3-43E2-AC6B-5229754C7678}" name="actual_cost" dataDxfId="9" dataCellStyle="Comma"/>
     <tableColumn id="10" xr3:uid="{7B805801-F707-4199-B930-DC0ABE2A33AF}" name="status" totalsRowFunction="count"/>
     <tableColumn id="11" xr3:uid="{3950F076-67D4-48CF-AEED-6EB579504530}" name="variance"/>
     <tableColumn id="12" xr3:uid="{B4D02EB1-68B9-4311-8D42-EEBDC2CC34B1}" name="margin_pct"/>
@@ -13176,13 +14362,13 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="budget"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="actual_cost"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="status"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="variance" dataDxfId="9">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="variance" dataDxfId="8">
       <calculatedColumnFormula>H2-I2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="margin_pct" dataDxfId="8">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="margin_pct" dataDxfId="7">
       <calculatedColumnFormula>K2/H2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="budget_with_uplift" dataDxfId="7">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="budget_with_uplift" dataDxfId="6">
       <calculatedColumnFormula>H2*(1+$T$2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13204,23 +14390,23 @@
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="budget"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="actual_cost"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="status"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="variance" dataDxfId="6">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="variance" dataDxfId="5">
       <calculatedColumnFormula>IF(ISBLANK(I2), "NO COST YET", H2-I2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="margin_pct" dataDxfId="5">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="margin_pct" dataDxfId="4">
       <calculatedColumnFormula>IF(ISBLANK(I2), "NO COST YET", K2/H2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="budget_with_uplift"/>
-    <tableColumn id="14" xr3:uid="{6ADA16E7-AD66-40BD-A05E-BB51EC772142}" name="client_name" dataDxfId="4">
+    <tableColumn id="14" xr3:uid="{6ADA16E7-AD66-40BD-A05E-BB51EC772142}" name="client_name" dataDxfId="3">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2, tblClients[client_id], tblClients[client_name], "CHECK CLIENT ID")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{C3B845C8-E030-43EF-9659-5C91666A6672}" name="risk_rating" dataDxfId="3">
+    <tableColumn id="15" xr3:uid="{C3B845C8-E030-43EF-9659-5C91666A6672}" name="risk_rating" dataDxfId="2">
       <calculatedColumnFormula>_xlfn.XLOOKUP(B2, tblClients[client_id], tblClients[risk_rating], "No Risk Rating")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{4A82E2C7-ECC2-4171-997E-328DE1C8B926}" name="id_count" dataDxfId="2">
+    <tableColumn id="16" xr3:uid="{4A82E2C7-ECC2-4171-997E-328DE1C8B926}" name="id_count" dataDxfId="1">
       <calculatedColumnFormula>COUNTIF(tblEng03[engagement_id], A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{7CEF5B5F-12BC-4339-9D42-68F689835FEF}" name="id_ok" dataDxfId="1">
+    <tableColumn id="17" xr3:uid="{7CEF5B5F-12BC-4339-9D42-68F689835FEF}" name="id_ok" dataDxfId="0">
       <calculatedColumnFormula>IF(LEN(A2)=8, "OK", "CHECK LENGTH")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -13244,28 +14430,6 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{F1DDF3AC-93B7-417A-B0D3-239E8A8A0515}" name="Table9" displayName="Table9" ref="A3:M8" totalsRowShown="0">
-  <autoFilter ref="A3:M8" xr:uid="{F1DDF3AC-93B7-417A-B0D3-239E8A8A0515}"/>
-  <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{74C15853-7B67-45FF-890A-42093AC3D96D}" name="txn_id"/>
-    <tableColumn id="2" xr3:uid="{D9392FE8-64E1-4364-9139-365F573DDFB2}" name="txn_date" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{1BD9F474-93E8-46C2-9D3E-970DAC9D24F0}" name="client_id"/>
-    <tableColumn id="4" xr3:uid="{4BA79A3B-4DA7-4267-9548-A5D7E53AA463}" name="txn_type"/>
-    <tableColumn id="5" xr3:uid="{5893F080-8600-488F-8D61-5E27FAD31B1D}" name="direction"/>
-    <tableColumn id="6" xr3:uid="{9D0DBFF4-BFEE-4972-9302-69DF39915DA0}" name="amount"/>
-    <tableColumn id="7" xr3:uid="{5B01F24B-61BE-4B8B-8333-9CB3C5F431FF}" name="currency"/>
-    <tableColumn id="8" xr3:uid="{A8904E36-02F7-4947-AA6F-138BE935BDAB}" name="channel"/>
-    <tableColumn id="9" xr3:uid="{6E41544D-8493-4A68-B65D-DA5A577687DD}" name="status"/>
-    <tableColumn id="10" xr3:uid="{E1DC2D92-59CF-4737-BB05-E702B09A905F}" name="counterparty"/>
-    <tableColumn id="11" xr3:uid="{DDF6FF2D-F203-4C46-BE0F-4FC4BC9EDA38}" name="country"/>
-    <tableColumn id="12" xr3:uid="{58A58F25-B962-4866-8EFF-071AAC3309BE}" name="client_name"/>
-    <tableColumn id="13" xr3:uid="{034641A3-E845-4961-81E2-E81D4DEFD1E9}" name="risk_rating"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="tblTxn" displayName="tblTxn" ref="A1:M301">
   <autoFilter ref="A1:M301" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="13">
@@ -13287,7 +14451,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="tblBank" displayName="tblBank" ref="A1:D121">
   <autoFilter ref="A1:D121" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="4">
@@ -13300,7 +14464,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="tblLedger" displayName="tblLedger" ref="J1:N122">
   <autoFilter ref="J1:N122" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="5">
@@ -13314,7 +14478,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="tblLabBank" displayName="tblLabBank" ref="N1:Q81">
   <autoFilter ref="N1:Q81" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
   <tableColumns count="4">
@@ -38152,285 +39316,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03DF21C8-786F-4925-ACA9-D46A5C99E513}">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
-        <v>2354</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F3" t="s">
-        <v>233</v>
-      </c>
-      <c r="G3" t="s">
-        <v>234</v>
-      </c>
-      <c r="H3" t="s">
-        <v>235</v>
-      </c>
-      <c r="I3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J3" t="s">
-        <v>1110</v>
-      </c>
-      <c r="K3" t="s">
-        <v>171</v>
-      </c>
-      <c r="L3" t="s">
-        <v>169</v>
-      </c>
-      <c r="M3" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1278</v>
-      </c>
-      <c r="B4" s="21">
-        <v>46078</v>
-      </c>
-      <c r="C4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" t="s">
-        <v>248</v>
-      </c>
-      <c r="E4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F4">
-        <v>8060</v>
-      </c>
-      <c r="G4" t="s">
-        <v>250</v>
-      </c>
-      <c r="H4" t="s">
-        <v>242</v>
-      </c>
-      <c r="I4" t="s">
-        <v>243</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1113</v>
-      </c>
-      <c r="K4" t="s">
-        <v>177</v>
-      </c>
-      <c r="L4" t="s">
-        <v>175</v>
-      </c>
-      <c r="M4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1271</v>
-      </c>
-      <c r="B5" s="21">
-        <v>46075</v>
-      </c>
-      <c r="C5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" t="s">
-        <v>248</v>
-      </c>
-      <c r="E5" t="s">
-        <v>239</v>
-      </c>
-      <c r="F5">
-        <v>18881</v>
-      </c>
-      <c r="G5" t="s">
-        <v>250</v>
-      </c>
-      <c r="H5" t="s">
-        <v>262</v>
-      </c>
-      <c r="I5" t="s">
-        <v>263</v>
-      </c>
-      <c r="J5" t="s">
-        <v>1121</v>
-      </c>
-      <c r="K5" t="s">
-        <v>188</v>
-      </c>
-      <c r="L5" t="s">
-        <v>175</v>
-      </c>
-      <c r="M5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>722</v>
-      </c>
-      <c r="B6" s="21">
-        <v>46073</v>
-      </c>
-      <c r="C6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" t="s">
-        <v>248</v>
-      </c>
-      <c r="E6" t="s">
-        <v>239</v>
-      </c>
-      <c r="F6">
-        <v>1366</v>
-      </c>
-      <c r="G6" t="s">
-        <v>250</v>
-      </c>
-      <c r="H6" t="s">
-        <v>251</v>
-      </c>
-      <c r="I6" t="s">
-        <v>243</v>
-      </c>
-      <c r="J6" t="s">
-        <v>1116</v>
-      </c>
-      <c r="K6" t="s">
-        <v>209</v>
-      </c>
-      <c r="L6" t="s">
-        <v>175</v>
-      </c>
-      <c r="M6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1259</v>
-      </c>
-      <c r="B7" s="21">
-        <v>46072</v>
-      </c>
-      <c r="C7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" t="s">
-        <v>248</v>
-      </c>
-      <c r="E7" t="s">
-        <v>281</v>
-      </c>
-      <c r="F7">
-        <v>18833</v>
-      </c>
-      <c r="G7" t="s">
-        <v>250</v>
-      </c>
-      <c r="H7" t="s">
-        <v>262</v>
-      </c>
-      <c r="I7" t="s">
-        <v>263</v>
-      </c>
-      <c r="J7" t="s">
-        <v>1121</v>
-      </c>
-      <c r="K7" t="s">
-        <v>188</v>
-      </c>
-      <c r="L7" t="s">
-        <v>175</v>
-      </c>
-      <c r="M7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>1247</v>
-      </c>
-      <c r="B8" s="21">
-        <v>46066</v>
-      </c>
-      <c r="C8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" t="s">
-        <v>248</v>
-      </c>
-      <c r="E8" t="s">
-        <v>239</v>
-      </c>
-      <c r="F8">
-        <v>8706</v>
-      </c>
-      <c r="G8" t="s">
-        <v>250</v>
-      </c>
-      <c r="H8" t="s">
-        <v>251</v>
-      </c>
-      <c r="I8" t="s">
-        <v>243</v>
-      </c>
-      <c r="J8" t="s">
-        <v>1116</v>
-      </c>
-      <c r="K8" t="s">
-        <v>209</v>
-      </c>
-      <c r="L8" t="s">
-        <v>175</v>
-      </c>
-      <c r="M8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21C3AED6-3435-452A-BC43-1C3C534DF251}">
   <dimension ref="A3:I31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -39259,6 +40144,136 @@
       </c>
       <c r="I31" s="29">
         <v>300</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A1ADAF-6366-484C-B45B-ED7A2B466B88}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2357</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2354</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2355</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="7">
+        <v>2003000</v>
+      </c>
+      <c r="C4" s="29">
+        <v>1490100</v>
+      </c>
+      <c r="D4" s="29">
+        <v>53900</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="7">
+        <v>2333000</v>
+      </c>
+      <c r="C5" s="29">
+        <v>2221400</v>
+      </c>
+      <c r="D5" s="29">
+        <v>111600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="7">
+        <v>2990000</v>
+      </c>
+      <c r="C6" s="29">
+        <v>1546500</v>
+      </c>
+      <c r="D6" s="29">
+        <v>239500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="7">
+        <v>2000500</v>
+      </c>
+      <c r="C7" s="29">
+        <v>1475600</v>
+      </c>
+      <c r="D7" s="29">
+        <v>232900</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="7">
+        <v>2318500</v>
+      </c>
+      <c r="C8" s="29">
+        <v>2113800</v>
+      </c>
+      <c r="D8" s="29">
+        <v>204700</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B9" s="7">
+        <v>11645000</v>
+      </c>
+      <c r="C9" s="29">
+        <v>8847400</v>
+      </c>
+      <c r="D9" s="29">
+        <v>842600</v>
       </c>
     </row>
   </sheetData>
